--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -331,31 +331,6 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>176</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7620000" cy="3810000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -648,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR9"/>
+  <dimension ref="A1:AR8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -657,8 +632,8 @@
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
     <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -666,8 +641,8 @@
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
     <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
@@ -675,8 +650,8 @@
     <col width="6" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
     <col width="5" customWidth="1" min="24" max="24"/>
-    <col width="5" customWidth="1" min="25" max="25"/>
-    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
@@ -684,15 +659,15 @@
     <col width="6" customWidth="1" min="31" max="31"/>
     <col width="5" customWidth="1" min="32" max="32"/>
     <col width="5" customWidth="1" min="33" max="33"/>
-    <col width="5" customWidth="1" min="34" max="34"/>
-    <col width="5" customWidth="1" min="35" max="35"/>
+    <col width="4" customWidth="1" min="34" max="34"/>
+    <col width="4" customWidth="1" min="35" max="35"/>
     <col width="2" customWidth="1" min="36" max="36"/>
     <col width="15" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
     <col width="6" customWidth="1" min="39" max="39"/>
     <col width="6" customWidth="1" min="40" max="40"/>
-    <col width="5" customWidth="1" min="41" max="41"/>
-    <col width="5" customWidth="1" min="42" max="42"/>
+    <col width="4" customWidth="1" min="41" max="41"/>
+    <col width="4" customWidth="1" min="42" max="42"/>
     <col width="4" customWidth="1" min="43" max="43"/>
     <col width="4" customWidth="1" min="44" max="44"/>
   </cols>
@@ -902,399 +877,399 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>30-March-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>335</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>25-March-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>335</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>24-March-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>335</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>23-March-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>30-March-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>25-March-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>24-March-2026</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>23-March-2026</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>78</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1306,184 +1281,184 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>30-March-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>25-March-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>24-March-2026</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>23-March-2026</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1496,7 +1471,7 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1508,197 +1483,197 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>30-March-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>25-March-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>24-March-2026</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>23-March-2026</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -1710,184 +1685,184 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>30-March-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>25-March-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>24-March-2026</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>23-March-2026</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>0</t>
@@ -1900,7 +1875,7 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -1912,540 +1887,402 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>30-March-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>25-March-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>24-March-2026</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>23-March-2026</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>30-March-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>206</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>740</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>743</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>25-March-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>197</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>749</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
         <is>
           <t>24-March-2026</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>23-March-2026</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AR8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v/>
-      </c>
-      <c r="B9" t="n">
-        <v/>
-      </c>
-      <c r="C9" t="n">
-        <v/>
-      </c>
-      <c r="D9" t="n">
-        <v/>
-      </c>
-      <c r="E9" t="n">
-        <v/>
-      </c>
-      <c r="F9" t="n">
-        <v/>
-      </c>
-      <c r="G9" t="n">
-        <v/>
-      </c>
-      <c r="H9" t="n">
-        <v/>
-      </c>
-      <c r="J9" t="n">
-        <v/>
-      </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
-      <c r="Q9" t="n">
-        <v/>
-      </c>
-      <c r="S9" t="n">
-        <v/>
-      </c>
-      <c r="T9" t="n">
-        <v/>
-      </c>
-      <c r="U9" t="n">
-        <v/>
-      </c>
-      <c r="V9" t="n">
-        <v/>
-      </c>
-      <c r="W9" t="n">
-        <v/>
-      </c>
-      <c r="X9" t="n">
-        <v/>
-      </c>
-      <c r="Y9" t="n">
-        <v/>
-      </c>
-      <c r="Z9" t="n">
-        <v/>
-      </c>
-      <c r="AB9" t="n">
-        <v/>
-      </c>
-      <c r="AC9" t="n">
-        <v/>
-      </c>
-      <c r="AD9" t="n">
-        <v/>
-      </c>
-      <c r="AE9" t="n">
-        <v/>
-      </c>
-      <c r="AF9" t="n">
-        <v/>
-      </c>
-      <c r="AG9" t="n">
-        <v/>
-      </c>
-      <c r="AH9" t="n">
-        <v/>
-      </c>
-      <c r="AI9" t="n">
-        <v/>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>23-March-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
         <is>
           <t>20</t>
         </is>

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -296,31 +296,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>154</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7620000" cy="3810000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -666,8 +641,8 @@
     <col width="16" customWidth="1" min="38" max="38"/>
     <col width="6" customWidth="1" min="39" max="39"/>
     <col width="6" customWidth="1" min="40" max="40"/>
-    <col width="4" customWidth="1" min="41" max="41"/>
-    <col width="4" customWidth="1" min="42" max="42"/>
+    <col width="5" customWidth="1" min="41" max="41"/>
+    <col width="5" customWidth="1" min="42" max="42"/>
     <col width="4" customWidth="1" min="43" max="43"/>
     <col width="4" customWidth="1" min="44" max="44"/>
   </cols>
@@ -877,167 +852,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>335</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>25-March-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>24-March-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1079,167 +1054,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>25-March-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>24-March-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1281,167 +1256,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>25-March-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>24-March-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1483,167 +1458,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>25-March-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>24-March-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1685,167 +1660,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>25-March-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>24-March-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1887,167 +1862,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>25-March-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>24-March-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2089,202 +2064,202 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>743</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>206</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>740</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>206</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>740</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>743</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
         <is>
           <t>25-March-2026</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>197</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>749</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>24-March-2026</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -852,167 +852,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>25-March-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1054,167 +1054,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>25-March-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1256,167 +1256,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>25-March-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1458,167 +1458,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>25-March-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1660,167 +1660,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>25-March-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1862,167 +1862,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>25-March-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2064,192 +2064,192 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>743</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>206</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>740</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>206</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>740</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>743</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>25-March-2026</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>749</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -852,184 +852,184 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1054,167 +1054,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>27-March-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1256,167 +1256,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>27-March-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1458,167 +1458,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>27-March-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1660,167 +1660,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1545</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1545</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>27-March-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1862,184 +1862,184 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>0</t>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -2064,192 +2064,192 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>741</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>743</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>206</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>740</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>206</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>740</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>743</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -852,167 +852,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>27-March-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1054,167 +1054,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>27-March-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1256,167 +1256,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>27-March-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1458,167 +1458,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>27-March-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1660,167 +1660,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1545</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1545</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1545</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1545</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>27-March-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1862,167 +1862,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>27-March-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2064,167 +2064,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>741</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>741</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>743</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
         <is>
           <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>27-March-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -852,167 +852,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>06-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1054,167 +1054,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>06-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1256,167 +1256,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>06-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1458,167 +1458,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>06-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1660,167 +1660,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>06-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1545</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1545</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1545</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1545</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>1545</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1545</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1862,167 +1862,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>06-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2064,192 +2064,192 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>06-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>743</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>741</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>741</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>741</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>743</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>740</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -852,167 +852,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1054,167 +1054,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1256,167 +1256,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1458,167 +1458,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1660,167 +1660,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1561</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1545</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1545</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>1545</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1545</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1545</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1545</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1862,167 +1862,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2064,192 +2064,192 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>742</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>743</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>741</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>741</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>741</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>743</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -852,167 +852,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1054,167 +1054,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1256,167 +1256,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1458,167 +1458,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1660,182 +1660,182 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1616</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1610</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1560</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>1545</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1545</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1545</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1545</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>1545</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>1545</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>1523</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1862,167 +1862,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2064,167 +2064,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>743</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>204</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>742</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>743</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>741</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
         <is>
           <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -852,167 +852,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1054,167 +1054,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1256,167 +1256,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1458,167 +1458,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1660,167 +1660,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1617</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1611</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1616</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1610</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1560</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1545</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1545</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>1545</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>1545</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1862,167 +1862,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2064,167 +2064,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>743</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>743</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>204</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>742</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>743</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
         <is>
           <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -852,167 +852,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1054,167 +1054,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1256,167 +1256,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1458,167 +1458,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1660,167 +1660,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1617</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1611</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1617</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1611</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>1616</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1610</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1560</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>1545</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>1545</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1862,167 +1862,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2064,192 +2064,192 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>743</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>743</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>743</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>204</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>742</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>743</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>741</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -852,167 +852,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>13-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1054,167 +1054,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>13-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1256,167 +1256,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>13-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1458,167 +1458,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>13-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1660,192 +1660,192 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>13-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1617</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1609</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1617</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1611</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>1617</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1611</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1616</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1610</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>1560</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>1545</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>1545</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1862,167 +1862,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>13-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2064,192 +2064,192 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>13-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>742</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>743</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>743</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>743</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>204</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>742</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>743</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -852,167 +852,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1054,167 +1054,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1256,167 +1256,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1458,167 +1458,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1660,192 +1660,192 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1561</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1558</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1617</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1609</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>1617</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1611</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1617</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1611</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>1616</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>1610</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>1561</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>1560</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1862,192 +1862,192 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -2064,192 +2064,192 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>204</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>742</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>743</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>743</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>743</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>742</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -852,167 +852,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>09-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1054,167 +1054,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>09-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1256,167 +1256,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>09-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1458,167 +1458,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>09-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1660,182 +1660,182 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1561</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1558</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1558</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>1617</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1609</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1617</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1611</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>1617</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>1611</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>1616</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>1610</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1862,167 +1862,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>09-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2064,167 +2064,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>206</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>740</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>204</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>742</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>743</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
         <is>
           <t>09-April-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>743</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -852,167 +852,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>10-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1054,167 +1054,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>10-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1256,167 +1256,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>10-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1458,167 +1458,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>10-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1660,167 +1660,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1561</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1558</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1558</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1558</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1617</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1609</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>10-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>1617</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>1611</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1862,167 +1862,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>10-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2064,167 +2064,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>741</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>206</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>740</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>204</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>742</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
         <is>
           <t>10-April-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>743</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -852,167 +852,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>10-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1054,167 +1054,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>10-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1256,167 +1256,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>10-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1458,167 +1458,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>10-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1660,192 +1660,192 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1561</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1558</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1558</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1558</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1558</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>1617</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>1609</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>10-April-2026</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>1617</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>1611</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1862,167 +1862,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>10-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2064,192 +2064,192 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>741</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>741</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>206</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>740</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>204</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>742</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>10-April-2026</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>743</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -852,167 +852,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1054,167 +1054,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1256,167 +1256,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1458,167 +1458,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1660,192 +1660,192 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1561</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1558</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1558</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1558</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1558</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>1558</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>1617</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>1609</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1862,167 +1862,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2064,192 +2064,192 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>202</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>744</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>741</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>741</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>206</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>740</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>742</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -852,167 +852,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1054,167 +1054,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1256,167 +1256,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1458,167 +1458,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1660,167 +1660,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1502</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1558</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1558</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1558</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>1561</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>1558</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1862,167 +1862,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2064,192 +2064,192 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>742</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>741</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>202</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>744</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>741</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>741</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>740</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -852,167 +852,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1054,167 +1054,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1256,167 +1256,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1458,167 +1458,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1660,167 +1660,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1561</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1539</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1502</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1558</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1558</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>1561</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>1558</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1862,167 +1862,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2064,167 +2064,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>204</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>742</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>741</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>202</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>744</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
         <is>
           <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -852,167 +852,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1054,167 +1054,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1256,167 +1256,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1458,167 +1458,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1660,167 +1660,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1586</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1562</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1539</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1502</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1558</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>1561</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>1558</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1862,167 +1862,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2064,192 +2064,192 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>514</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>206</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>740</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>204</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>742</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>741</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>202</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>744</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>741</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -852,167 +852,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>224</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1054,167 +1054,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1256,167 +1256,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1458,167 +1458,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1660,167 +1660,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1586</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1562</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1586</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1562</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1539</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1502</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>1561</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>1558</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1862,167 +1862,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>146</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2064,192 +2064,192 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>514</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>153</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>514</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>490</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>206</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>740</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>204</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>742</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>741</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>744</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -852,167 +852,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>27-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>224</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>224</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1054,167 +1054,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>27-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1256,167 +1256,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>27-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1458,167 +1458,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>27-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1660,192 +1660,192 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>27-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1723</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1695</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1586</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1562</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>1586</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1562</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1539</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>1502</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>1561</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>1558</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1862,167 +1862,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>27-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>231</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>146</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2064,192 +2064,192 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>27-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>514</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>148</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>514</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>495</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>153</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>514</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>490</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>206</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>740</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>204</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>742</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>741</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -852,167 +852,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>224</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>224</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>224</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1054,167 +1054,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1256,167 +1256,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1458,167 +1458,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1660,192 +1660,192 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1723</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1717</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1723</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1695</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>1586</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1562</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1586</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1562</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>1561</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>1539</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>1502</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1862,167 +1862,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>231</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>231</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>146</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2064,192 +2064,192 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>514</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>488</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>148</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>514</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>495</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>153</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>514</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>490</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>206</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>740</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>742</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -559,6 +559,15 @@
     <col width="5" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="2" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -602,44 +611,124 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -648,40 +737,80 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -690,40 +819,80 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -732,40 +901,80 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1713</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>1713</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -774,40 +983,80 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>741</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -655,47 +655,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -737,47 +737,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -819,47 +819,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -901,47 +901,47 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1713</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -983,72 +983,72 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>735</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>208</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>738</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>741</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -559,15 +559,6 @@
     <col width="5" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
-    <col width="2" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -611,51 +602,11 @@
           <t>KI</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -689,46 +640,6 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -737,7 +648,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -771,46 +682,6 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -819,7 +690,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -853,46 +724,6 @@
         </is>
       </c>
       <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -901,7 +732,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -935,46 +766,6 @@
         </is>
       </c>
       <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -983,7 +774,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -998,17 +789,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>737</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1017,46 +808,6 @@
         </is>
       </c>
       <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>738</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -559,6 +559,15 @@
     <col width="5" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="2" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -602,44 +611,124 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -648,40 +737,80 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -690,40 +819,80 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -732,40 +901,80 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>1713</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -774,40 +983,80 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>737</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -568,6 +568,15 @@
     <col width="5" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -651,84 +660,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -737,80 +826,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -819,80 +948,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -901,80 +1070,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1789</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>1701</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>1713</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -983,80 +1192,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>207</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>739</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>737</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -246,6 +246,56 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>110</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>132</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -548,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:AI8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -557,8 +607,8 @@
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
     <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="4" customWidth="1" min="7" max="7"/>
-    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -575,8 +625,17 @@
     <col width="6" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
     <col width="5" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="6" customWidth="1" min="30" max="30"/>
+    <col width="6" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -700,124 +759,204 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -826,104 +965,104 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
       <c r="W3" t="inlineStr">
         <is>
           <t>0</t>
@@ -943,241 +1082,289 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB3" t="n">
+        <v/>
+      </c>
+      <c r="AC3" t="n">
+        <v/>
+      </c>
+      <c r="AD3" t="n">
+        <v/>
+      </c>
+      <c r="AE3" t="n">
+        <v/>
+      </c>
+      <c r="AF3" t="n">
+        <v/>
+      </c>
+      <c r="AG3" t="n">
+        <v/>
+      </c>
+      <c r="AH3" t="n">
+        <v/>
+      </c>
+      <c r="AI3" t="n">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB4" t="n">
+        <v/>
+      </c>
+      <c r="AC4" t="n">
+        <v/>
+      </c>
+      <c r="AD4" t="n">
+        <v/>
+      </c>
+      <c r="AE4" t="n">
+        <v/>
+      </c>
+      <c r="AF4" t="n">
+        <v/>
+      </c>
+      <c r="AG4" t="n">
+        <v/>
+      </c>
+      <c r="AH4" t="n">
+        <v/>
+      </c>
+      <c r="AI4" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1770</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1789</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>1734</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>1701</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
           <t>0</t>
@@ -1187,128 +1374,420 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB5" t="n">
+        <v/>
+      </c>
+      <c r="AC5" t="n">
+        <v/>
+      </c>
+      <c r="AD5" t="n">
+        <v/>
+      </c>
+      <c r="AE5" t="n">
+        <v/>
+      </c>
+      <c r="AF5" t="n">
+        <v/>
+      </c>
+      <c r="AG5" t="n">
+        <v/>
+      </c>
+      <c r="AH5" t="n">
+        <v/>
+      </c>
+      <c r="AI5" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1789</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>207</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>739</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v/>
+      </c>
+      <c r="T7" t="n">
+        <v/>
+      </c>
+      <c r="U7" t="n">
+        <v/>
+      </c>
+      <c r="V7" t="n">
+        <v/>
+      </c>
+      <c r="W7" t="n">
+        <v/>
+      </c>
+      <c r="X7" t="n">
+        <v/>
+      </c>
+      <c r="Y7" t="n">
+        <v/>
+      </c>
+      <c r="Z7" t="n">
+        <v/>
+      </c>
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v/>
+      </c>
+      <c r="B8" t="n">
+        <v/>
+      </c>
+      <c r="C8" t="n">
+        <v/>
+      </c>
+      <c r="D8" t="n">
+        <v/>
+      </c>
+      <c r="E8" t="n">
+        <v/>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>207</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>739</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>737</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v/>
+      </c>
+      <c r="T8" t="n">
+        <v/>
+      </c>
+      <c r="U8" t="n">
+        <v/>
+      </c>
+      <c r="V8" t="n">
+        <v/>
+      </c>
+      <c r="W8" t="n">
+        <v/>
+      </c>
+      <c r="X8" t="n">
+        <v/>
+      </c>
+      <c r="Y8" t="n">
+        <v/>
+      </c>
+      <c r="Z8" t="n">
+        <v/>
+      </c>
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -616,8 +616,8 @@
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
     <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
@@ -625,8 +625,8 @@
     <col width="6" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
     <col width="5" customWidth="1" min="24" max="24"/>
-    <col width="5" customWidth="1" min="25" max="25"/>
-    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="9" customWidth="1" min="29" max="29"/>
@@ -803,129 +803,129 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>305</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>partner</t>
@@ -933,22 +933,22 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1734</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -965,117 +965,117 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1111,104 +1111,104 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1257,117 +1257,117 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1795</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>1800</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>1770</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1403,112 +1403,112 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>1789</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1729</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>59</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>739</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1549,107 +1549,123 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>208</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>738</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
-      </c>
-      <c r="S7" t="n">
-        <v/>
-      </c>
-      <c r="T7" t="n">
-        <v/>
-      </c>
-      <c r="U7" t="n">
-        <v/>
-      </c>
-      <c r="V7" t="n">
-        <v/>
-      </c>
-      <c r="W7" t="n">
-        <v/>
-      </c>
-      <c r="X7" t="n">
-        <v/>
-      </c>
-      <c r="Y7" t="n">
-        <v/>
-      </c>
-      <c r="Z7" t="n">
-        <v/>
       </c>
       <c r="AB7" t="n">
         <v/>
@@ -1701,69 +1717,69 @@
       <c r="H8" t="n">
         <v/>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" t="n">
+        <v/>
+      </c>
+      <c r="K8" t="n">
+        <v/>
+      </c>
+      <c r="L8" t="n">
+        <v/>
+      </c>
+      <c r="M8" t="n">
+        <v/>
+      </c>
+      <c r="N8" t="n">
+        <v/>
+      </c>
+      <c r="O8" t="n">
+        <v/>
+      </c>
+      <c r="P8" t="n">
+        <v/>
+      </c>
+      <c r="Q8" t="n">
+        <v/>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>207</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>739</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="n">
-        <v/>
-      </c>
-      <c r="T8" t="n">
-        <v/>
-      </c>
-      <c r="U8" t="n">
-        <v/>
-      </c>
-      <c r="V8" t="n">
-        <v/>
-      </c>
-      <c r="W8" t="n">
-        <v/>
-      </c>
-      <c r="X8" t="n">
-        <v/>
-      </c>
-      <c r="Y8" t="n">
-        <v/>
-      </c>
-      <c r="Z8" t="n">
-        <v/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="AB8" t="n">
         <v/>

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -271,31 +271,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>132</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7620000" cy="3810000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -598,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -607,35 +582,17 @@
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
     <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
     <col width="5" customWidth="1" min="15" max="15"/>
     <col width="5" customWidth="1" min="16" max="16"/>
     <col width="5" customWidth="1" min="17" max="17"/>
-    <col width="2" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="6" customWidth="1" min="22" max="22"/>
-    <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="5" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
-    <col width="2" customWidth="1" min="27" max="27"/>
-    <col width="13" customWidth="1" min="28" max="28"/>
-    <col width="9" customWidth="1" min="29" max="29"/>
-    <col width="6" customWidth="1" min="30" max="30"/>
-    <col width="6" customWidth="1" min="31" max="31"/>
-    <col width="5" customWidth="1" min="32" max="32"/>
-    <col width="5" customWidth="1" min="33" max="33"/>
-    <col width="5" customWidth="1" min="34" max="34"/>
-    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -719,146 +676,66 @@
           <t>KI</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>18-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>15-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>masterdata-ara</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -868,95 +745,15 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>1789</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -965,7 +762,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1003,115 +800,35 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v/>
-      </c>
-      <c r="AC3" t="n">
-        <v/>
-      </c>
-      <c r="AD3" t="n">
-        <v/>
-      </c>
-      <c r="AE3" t="n">
-        <v/>
-      </c>
-      <c r="AF3" t="n">
-        <v/>
-      </c>
-      <c r="AG3" t="n">
-        <v/>
-      </c>
-      <c r="AH3" t="n">
-        <v/>
-      </c>
-      <c r="AI3" t="n">
+      <c r="J3" t="n">
+        <v/>
+      </c>
+      <c r="K3" t="n">
+        <v/>
+      </c>
+      <c r="L3" t="n">
+        <v/>
+      </c>
+      <c r="M3" t="n">
+        <v/>
+      </c>
+      <c r="N3" t="n">
+        <v/>
+      </c>
+      <c r="O3" t="n">
+        <v/>
+      </c>
+      <c r="P3" t="n">
+        <v/>
+      </c>
+      <c r="Q3" t="n">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1149,115 +866,35 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v/>
-      </c>
-      <c r="AC4" t="n">
-        <v/>
-      </c>
-      <c r="AD4" t="n">
-        <v/>
-      </c>
-      <c r="AE4" t="n">
-        <v/>
-      </c>
-      <c r="AF4" t="n">
-        <v/>
-      </c>
-      <c r="AG4" t="n">
-        <v/>
-      </c>
-      <c r="AH4" t="n">
-        <v/>
-      </c>
-      <c r="AI4" t="n">
+      <c r="J4" t="n">
+        <v/>
+      </c>
+      <c r="K4" t="n">
+        <v/>
+      </c>
+      <c r="L4" t="n">
+        <v/>
+      </c>
+      <c r="M4" t="n">
+        <v/>
+      </c>
+      <c r="N4" t="n">
+        <v/>
+      </c>
+      <c r="O4" t="n">
+        <v/>
+      </c>
+      <c r="P4" t="n">
+        <v/>
+      </c>
+      <c r="Q4" t="n">
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1295,115 +932,35 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>1770</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v/>
-      </c>
-      <c r="AC5" t="n">
-        <v/>
-      </c>
-      <c r="AD5" t="n">
-        <v/>
-      </c>
-      <c r="AE5" t="n">
-        <v/>
-      </c>
-      <c r="AF5" t="n">
-        <v/>
-      </c>
-      <c r="AG5" t="n">
-        <v/>
-      </c>
-      <c r="AH5" t="n">
-        <v/>
-      </c>
-      <c r="AI5" t="n">
+      <c r="J5" t="n">
+        <v/>
+      </c>
+      <c r="K5" t="n">
+        <v/>
+      </c>
+      <c r="L5" t="n">
+        <v/>
+      </c>
+      <c r="M5" t="n">
+        <v/>
+      </c>
+      <c r="N5" t="n">
+        <v/>
+      </c>
+      <c r="O5" t="n">
+        <v/>
+      </c>
+      <c r="P5" t="n">
+        <v/>
+      </c>
+      <c r="Q5" t="n">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1441,115 +998,35 @@
           <t>4</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>1789</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v/>
-      </c>
-      <c r="AC6" t="n">
-        <v/>
-      </c>
-      <c r="AD6" t="n">
-        <v/>
-      </c>
-      <c r="AE6" t="n">
-        <v/>
-      </c>
-      <c r="AF6" t="n">
-        <v/>
-      </c>
-      <c r="AG6" t="n">
-        <v/>
-      </c>
-      <c r="AH6" t="n">
-        <v/>
-      </c>
-      <c r="AI6" t="n">
+      <c r="J6" t="n">
+        <v/>
+      </c>
+      <c r="K6" t="n">
+        <v/>
+      </c>
+      <c r="L6" t="n">
+        <v/>
+      </c>
+      <c r="M6" t="n">
+        <v/>
+      </c>
+      <c r="N6" t="n">
+        <v/>
+      </c>
+      <c r="O6" t="n">
+        <v/>
+      </c>
+      <c r="P6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" t="n">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1587,222 +1064,28 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>738</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v/>
-      </c>
-      <c r="AC7" t="n">
-        <v/>
-      </c>
-      <c r="AD7" t="n">
-        <v/>
-      </c>
-      <c r="AE7" t="n">
-        <v/>
-      </c>
-      <c r="AF7" t="n">
-        <v/>
-      </c>
-      <c r="AG7" t="n">
-        <v/>
-      </c>
-      <c r="AH7" t="n">
-        <v/>
-      </c>
-      <c r="AI7" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v/>
-      </c>
-      <c r="B8" t="n">
-        <v/>
-      </c>
-      <c r="C8" t="n">
-        <v/>
-      </c>
-      <c r="D8" t="n">
-        <v/>
-      </c>
-      <c r="E8" t="n">
-        <v/>
-      </c>
-      <c r="F8" t="n">
-        <v/>
-      </c>
-      <c r="G8" t="n">
-        <v/>
-      </c>
-      <c r="H8" t="n">
-        <v/>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
-        <v/>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>739</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v/>
-      </c>
-      <c r="AC8" t="n">
-        <v/>
-      </c>
-      <c r="AD8" t="n">
-        <v/>
-      </c>
-      <c r="AE8" t="n">
-        <v/>
-      </c>
-      <c r="AF8" t="n">
-        <v/>
-      </c>
-      <c r="AG8" t="n">
-        <v/>
-      </c>
-      <c r="AH8" t="n">
-        <v/>
-      </c>
-      <c r="AI8" t="n">
+      <c r="J7" t="n">
+        <v/>
+      </c>
+      <c r="K7" t="n">
+        <v/>
+      </c>
+      <c r="L7" t="n">
+        <v/>
+      </c>
+      <c r="M7" t="n">
+        <v/>
+      </c>
+      <c r="N7" t="n">
+        <v/>
+      </c>
+      <c r="O7" t="n">
+        <v/>
+      </c>
+      <c r="P7" t="n">
+        <v/>
+      </c>
+      <c r="Q7" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -586,13 +586,13 @@
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
     <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -680,77 +680,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>15-May-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>1795</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -762,331 +762,411 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v/>
-      </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
-      <c r="Q3" t="n">
-        <v/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v/>
-      </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
-      <c r="Q4" t="n">
-        <v/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1795</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>1800</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>1795</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
-      <c r="L5" t="n">
-        <v/>
-      </c>
-      <c r="M5" t="n">
-        <v/>
-      </c>
-      <c r="N5" t="n">
-        <v/>
-      </c>
-      <c r="O5" t="n">
-        <v/>
-      </c>
-      <c r="P5" t="n">
-        <v/>
-      </c>
-      <c r="Q5" t="n">
-        <v/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
-        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>743</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>206</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>740</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
-        <v/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -271,6 +271,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>132</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -573,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -591,8 +616,17 @@
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
     <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -676,84 +710,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -762,80 +876,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -844,80 +998,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -926,80 +1120,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>1800</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>1795</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>1800</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>1795</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1008,80 +1242,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1795</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1090,83 +1364,213 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>743</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>206</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>740</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v/>
+      </c>
+      <c r="K8" t="n">
+        <v/>
+      </c>
+      <c r="L8" t="n">
+        <v/>
+      </c>
+      <c r="M8" t="n">
+        <v/>
+      </c>
+      <c r="N8" t="n">
+        <v/>
+      </c>
+      <c r="O8" t="n">
+        <v/>
+      </c>
+      <c r="P8" t="n">
+        <v/>
+      </c>
+      <c r="Q8" t="n">
+        <v/>
+      </c>
+      <c r="S8" t="n">
+        <v/>
+      </c>
+      <c r="T8" t="n">
+        <v/>
+      </c>
+      <c r="U8" t="n">
+        <v/>
+      </c>
+      <c r="V8" t="n">
+        <v/>
+      </c>
+      <c r="W8" t="n">
+        <v/>
+      </c>
+      <c r="X8" t="n">
+        <v/>
+      </c>
+      <c r="Y8" t="n">
+        <v/>
+      </c>
+      <c r="Z8" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/dev.xlsx
+++ b/minio-report-tracker/xlxs/dev.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:AI8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -616,8 +616,8 @@
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
     <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
@@ -627,6 +627,15 @@
     <col width="5" customWidth="1" min="24" max="24"/>
     <col width="5" customWidth="1" min="25" max="25"/>
     <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -750,230 +759,310 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>270</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
       <c r="W3" t="inlineStr">
         <is>
           <t>0</t>
@@ -993,241 +1082,289 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB3" t="n">
+        <v/>
+      </c>
+      <c r="AC3" t="n">
+        <v/>
+      </c>
+      <c r="AD3" t="n">
+        <v/>
+      </c>
+      <c r="AE3" t="n">
+        <v/>
+      </c>
+      <c r="AF3" t="n">
+        <v/>
+      </c>
+      <c r="AG3" t="n">
+        <v/>
+      </c>
+      <c r="AH3" t="n">
+        <v/>
+      </c>
+      <c r="AI3" t="n">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB4" t="n">
+        <v/>
+      </c>
+      <c r="AC4" t="n">
+        <v/>
+      </c>
+      <c r="AD4" t="n">
+        <v/>
+      </c>
+      <c r="AE4" t="n">
+        <v/>
+      </c>
+      <c r="AF4" t="n">
+        <v/>
+      </c>
+      <c r="AG4" t="n">
+        <v/>
+      </c>
+      <c r="AH4" t="n">
+        <v/>
+      </c>
+      <c r="AI4" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>1800</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>1795</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>1795</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
           <t>0</t>
@@ -1237,241 +1374,289 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB5" t="n">
+        <v/>
+      </c>
+      <c r="AC5" t="n">
+        <v/>
+      </c>
+      <c r="AD5" t="n">
+        <v/>
+      </c>
+      <c r="AE5" t="n">
+        <v/>
+      </c>
+      <c r="AF5" t="n">
+        <v/>
+      </c>
+      <c r="AG5" t="n">
+        <v/>
+      </c>
+      <c r="AH5" t="n">
+        <v/>
+      </c>
+      <c r="AI5" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1795</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1800</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1795</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>743</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
           <t>0</t>
@@ -1481,72 +1666,112 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1157</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>207</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>739</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
-        <v/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="S8" t="n">
         <v/>
@@ -1570,6 +1795,30 @@
         <v/>
       </c>
       <c r="Z8" t="n">
+        <v/>
+      </c>
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
         <v/>
       </c>
     </row>
